--- a/output/yearly_total_coral_cover_iteration_67_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_67_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.27386323392653</v>
+        <v>1.264703527845907</v>
       </c>
       <c r="C3" t="n">
-        <v>4.720220272881628</v>
+        <v>4.67022967978138</v>
       </c>
       <c r="D3" t="n">
-        <v>6.057201805812174</v>
+        <v>6.028191161151681</v>
       </c>
       <c r="E3" t="n">
-        <v>12.05128531262033</v>
+        <v>11.96312436877897</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.422541315787208</v>
+        <v>1.405886356484625</v>
       </c>
       <c r="C4" t="n">
-        <v>5.402961463489174</v>
+        <v>5.238853117882814</v>
       </c>
       <c r="D4" t="n">
-        <v>6.25805645665443</v>
+        <v>6.196070685045407</v>
       </c>
       <c r="E4" t="n">
-        <v>13.08355923593081</v>
+        <v>12.84081015941285</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.632905557112313</v>
+        <v>1.602956871621899</v>
       </c>
       <c r="C5" t="n">
-        <v>6.301312395259846</v>
+        <v>5.983726781966443</v>
       </c>
       <c r="D5" t="n">
-        <v>6.618294849980506</v>
+        <v>6.445000262871588</v>
       </c>
       <c r="E5" t="n">
-        <v>14.55251280235266</v>
+        <v>14.03168391645993</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.864804136446351</v>
+        <v>1.823956445101869</v>
       </c>
       <c r="C6" t="n">
-        <v>7.403101797078783</v>
+        <v>6.910803215649167</v>
       </c>
       <c r="D6" t="n">
-        <v>7.062782297810101</v>
+        <v>6.693788554852219</v>
       </c>
       <c r="E6" t="n">
-        <v>16.33068823133523</v>
+        <v>15.42854821560325</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.118984513192617</v>
+        <v>2.068677686081036</v>
       </c>
       <c r="C7" t="n">
-        <v>8.636976698849596</v>
+        <v>8.035570690709742</v>
       </c>
       <c r="D7" t="n">
-        <v>7.531251678924224</v>
+        <v>6.965442567046032</v>
       </c>
       <c r="E7" t="n">
-        <v>18.28721289096644</v>
+        <v>17.06969094383681</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.313066140427796</v>
+        <v>1.26984332200504</v>
       </c>
       <c r="C8" t="n">
-        <v>6.21688124599273</v>
+        <v>5.772674536454942</v>
       </c>
       <c r="D8" t="n">
-        <v>5.924586120082733</v>
+        <v>5.125276564712241</v>
       </c>
       <c r="E8" t="n">
-        <v>13.45453350650326</v>
+        <v>12.16779442317222</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.633701817821245</v>
+        <v>1.580907880160731</v>
       </c>
       <c r="C9" t="n">
-        <v>7.695087065713285</v>
+        <v>7.25975946188899</v>
       </c>
       <c r="D9" t="n">
-        <v>6.581640295982057</v>
+        <v>5.467053139911273</v>
       </c>
       <c r="E9" t="n">
-        <v>15.91042917951659</v>
+        <v>14.30772048196099</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.958220826632756</v>
+        <v>1.908266708483863</v>
       </c>
       <c r="C10" t="n">
-        <v>9.289254390386603</v>
+        <v>8.946750980571474</v>
       </c>
       <c r="D10" t="n">
-        <v>7.175860451671047</v>
+        <v>5.886259318706727</v>
       </c>
       <c r="E10" t="n">
-        <v>18.42333566869041</v>
+        <v>16.74127700776206</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.271080527406159</v>
+        <v>2.241804973420234</v>
       </c>
       <c r="C11" t="n">
-        <v>10.94314218543994</v>
+        <v>10.81523313882253</v>
       </c>
       <c r="D11" t="n">
-        <v>7.812810698430384</v>
+        <v>6.264752276736399</v>
       </c>
       <c r="E11" t="n">
-        <v>21.02703341127648</v>
+        <v>19.32179038897917</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.554978417911018</v>
+        <v>2.568692464749077</v>
       </c>
       <c r="C12" t="n">
-        <v>12.68689416643001</v>
+        <v>12.76027706734047</v>
       </c>
       <c r="D12" t="n">
-        <v>8.331850619703635</v>
+        <v>6.694724936657704</v>
       </c>
       <c r="E12" t="n">
-        <v>23.57372320404466</v>
+        <v>22.02369446874726</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.80126211896338</v>
+        <v>2.881334470461286</v>
       </c>
       <c r="C13" t="n">
-        <v>14.39987396126478</v>
+        <v>14.74602535283602</v>
       </c>
       <c r="D13" t="n">
-        <v>8.887996294535263</v>
+        <v>7.124003755170444</v>
       </c>
       <c r="E13" t="n">
-        <v>26.08913237476342</v>
+        <v>24.75136357846775</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.598805588797058</v>
+        <v>1.666212386170644</v>
       </c>
       <c r="C14" t="n">
-        <v>10.05874154078676</v>
+        <v>10.25876281805</v>
       </c>
       <c r="D14" t="n">
-        <v>6.772714164948174</v>
+        <v>5.471034518841413</v>
       </c>
       <c r="E14" t="n">
-        <v>18.43026129453199</v>
+        <v>17.39600972306206</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.590843614915616</v>
+        <v>1.699611443069121</v>
       </c>
       <c r="C15" t="n">
-        <v>10.80207181505723</v>
+        <v>11.26051854050936</v>
       </c>
       <c r="D15" t="n">
-        <v>6.839679175854848</v>
+        <v>5.429742210400792</v>
       </c>
       <c r="E15" t="n">
-        <v>19.2325946058277</v>
+        <v>18.38987219397928</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.806739752556533</v>
+        <v>1.954532051953848</v>
       </c>
       <c r="C16" t="n">
-        <v>12.69263318660235</v>
+        <v>13.38429407919832</v>
       </c>
       <c r="D16" t="n">
-        <v>7.313431348016189</v>
+        <v>5.801814772833291</v>
       </c>
       <c r="E16" t="n">
-        <v>21.81280428717508</v>
+        <v>21.14064090398546</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.422650598224053</v>
+        <v>1.552584906881118</v>
       </c>
       <c r="C17" t="n">
-        <v>11.57527667196793</v>
+        <v>12.33596424564949</v>
       </c>
       <c r="D17" t="n">
-        <v>6.809127187298688</v>
+        <v>5.318078226519759</v>
       </c>
       <c r="E17" t="n">
-        <v>19.80705445749067</v>
+        <v>19.20662737905037</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.59455462123767</v>
+        <v>1.749651123554581</v>
       </c>
       <c r="C18" t="n">
-        <v>13.50431273604249</v>
+        <v>14.41410815104505</v>
       </c>
       <c r="D18" t="n">
-        <v>7.278471312267961</v>
+        <v>5.672646227385537</v>
       </c>
       <c r="E18" t="n">
-        <v>22.37733866954812</v>
+        <v>21.83640550198517</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.572210043489012</v>
+        <v>1.734227867120863</v>
       </c>
       <c r="C19" t="n">
-        <v>14.42938414532314</v>
+        <v>15.39215466644685</v>
       </c>
       <c r="D19" t="n">
-        <v>7.383979738043365</v>
+        <v>5.731600177025559</v>
       </c>
       <c r="E19" t="n">
-        <v>23.38557392685551</v>
+        <v>22.85798271059327</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.721268797424805</v>
+        <v>1.901507858447477</v>
       </c>
       <c r="C20" t="n">
-        <v>16.59572826446823</v>
+        <v>17.54824933955961</v>
       </c>
       <c r="D20" t="n">
-        <v>7.794212833739938</v>
+        <v>6.088062950960533</v>
       </c>
       <c r="E20" t="n">
-        <v>26.11120989563297</v>
+        <v>25.53782014896762</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.011848088859018</v>
+        <v>1.114813788080423</v>
       </c>
       <c r="C21" t="n">
-        <v>12.24725352309375</v>
+        <v>12.73699836535727</v>
       </c>
       <c r="D21" t="n">
-        <v>6.529711973193003</v>
+        <v>5.073092904402011</v>
       </c>
       <c r="E21" t="n">
-        <v>19.78881358514577</v>
+        <v>18.9249050578397</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_67_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_67_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.264703527845907</v>
+        <v>1.254984225573864</v>
       </c>
       <c r="C3" t="n">
-        <v>4.67022967978138</v>
+        <v>4.698081862150863</v>
       </c>
       <c r="D3" t="n">
-        <v>6.028191161151681</v>
+        <v>6.111757525737169</v>
       </c>
       <c r="E3" t="n">
-        <v>11.96312436877897</v>
+        <v>12.0648236134619</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.405886356484625</v>
+        <v>1.373441796763086</v>
       </c>
       <c r="C4" t="n">
-        <v>5.238853117882814</v>
+        <v>5.329897490122534</v>
       </c>
       <c r="D4" t="n">
-        <v>6.196070685045407</v>
+        <v>6.349152553621522</v>
       </c>
       <c r="E4" t="n">
-        <v>12.84081015941285</v>
+        <v>13.05249184050714</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.602956871621899</v>
+        <v>1.526948738202094</v>
       </c>
       <c r="C5" t="n">
-        <v>5.983726781966443</v>
+        <v>6.166801420282106</v>
       </c>
       <c r="D5" t="n">
-        <v>6.445000262871588</v>
+        <v>6.654394389025481</v>
       </c>
       <c r="E5" t="n">
-        <v>14.03168391645993</v>
+        <v>14.34814454750968</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.823956445101869</v>
+        <v>1.702397402004481</v>
       </c>
       <c r="C6" t="n">
-        <v>6.910803215649167</v>
+        <v>7.215844941211537</v>
       </c>
       <c r="D6" t="n">
-        <v>6.693788554852219</v>
+        <v>6.980876033912711</v>
       </c>
       <c r="E6" t="n">
-        <v>15.42854821560325</v>
+        <v>15.89911837712873</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.068677686081036</v>
+        <v>1.907450920612722</v>
       </c>
       <c r="C7" t="n">
-        <v>8.035570690709742</v>
+        <v>8.410482366352321</v>
       </c>
       <c r="D7" t="n">
-        <v>6.965442567046032</v>
+        <v>7.407536300812112</v>
       </c>
       <c r="E7" t="n">
-        <v>17.06969094383681</v>
+        <v>17.72546958777716</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.26984332200504</v>
+        <v>1.142854002831163</v>
       </c>
       <c r="C8" t="n">
-        <v>5.772674536454942</v>
+        <v>6.053361190429841</v>
       </c>
       <c r="D8" t="n">
-        <v>5.125276564712241</v>
+        <v>5.692852760021974</v>
       </c>
       <c r="E8" t="n">
-        <v>12.16779442317222</v>
+        <v>12.88906795328298</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.580907880160731</v>
+        <v>1.405225046978015</v>
       </c>
       <c r="C9" t="n">
-        <v>7.25975946188899</v>
+        <v>7.535759133048591</v>
       </c>
       <c r="D9" t="n">
-        <v>5.467053139911273</v>
+        <v>6.248807309824381</v>
       </c>
       <c r="E9" t="n">
-        <v>14.30772048196099</v>
+        <v>15.18979148985099</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.908266708483863</v>
+        <v>1.680698703831814</v>
       </c>
       <c r="C10" t="n">
-        <v>8.946750980571474</v>
+        <v>9.188909120868754</v>
       </c>
       <c r="D10" t="n">
-        <v>5.886259318706727</v>
+        <v>6.769566374278499</v>
       </c>
       <c r="E10" t="n">
-        <v>16.74127700776206</v>
+        <v>17.63917419897907</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.241804973420234</v>
+        <v>1.94275814740336</v>
       </c>
       <c r="C11" t="n">
-        <v>10.81523313882253</v>
+        <v>10.95153936054111</v>
       </c>
       <c r="D11" t="n">
-        <v>6.264752276736399</v>
+        <v>7.248515440234823</v>
       </c>
       <c r="E11" t="n">
-        <v>19.32179038897917</v>
+        <v>20.1428129481793</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.568692464749077</v>
+        <v>2.210565428930182</v>
       </c>
       <c r="C12" t="n">
-        <v>12.76027706734047</v>
+        <v>12.82444417221617</v>
       </c>
       <c r="D12" t="n">
-        <v>6.694724936657704</v>
+        <v>7.699513585968435</v>
       </c>
       <c r="E12" t="n">
-        <v>22.02369446874726</v>
+        <v>22.73452318711479</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.881334470461286</v>
+        <v>2.450393552169631</v>
       </c>
       <c r="C13" t="n">
-        <v>14.74602535283602</v>
+        <v>14.69164580939835</v>
       </c>
       <c r="D13" t="n">
-        <v>7.124003755170444</v>
+        <v>8.136632168959167</v>
       </c>
       <c r="E13" t="n">
-        <v>24.75136357846775</v>
+        <v>25.27867153052715</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.666212386170644</v>
+        <v>1.404154471476043</v>
       </c>
       <c r="C14" t="n">
-        <v>10.25876281805</v>
+        <v>10.25425659608751</v>
       </c>
       <c r="D14" t="n">
-        <v>5.471034518841413</v>
+        <v>6.172110371921102</v>
       </c>
       <c r="E14" t="n">
-        <v>17.39600972306206</v>
+        <v>17.83052143948466</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.699611443069121</v>
+        <v>1.419155576396935</v>
       </c>
       <c r="C15" t="n">
-        <v>11.26051854050936</v>
+        <v>11.14070605068308</v>
       </c>
       <c r="D15" t="n">
-        <v>5.429742210400792</v>
+        <v>6.159504731398573</v>
       </c>
       <c r="E15" t="n">
-        <v>18.38987219397928</v>
+        <v>18.71936635847859</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.954532051953848</v>
+        <v>1.620109513979214</v>
       </c>
       <c r="C16" t="n">
-        <v>13.38429407919832</v>
+        <v>13.19130211549748</v>
       </c>
       <c r="D16" t="n">
-        <v>5.801814772833291</v>
+        <v>6.560548668583396</v>
       </c>
       <c r="E16" t="n">
-        <v>21.14064090398546</v>
+        <v>21.37196029806009</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.552584906881118</v>
+        <v>1.285107744859075</v>
       </c>
       <c r="C17" t="n">
-        <v>12.33596424564949</v>
+        <v>12.13250685142138</v>
       </c>
       <c r="D17" t="n">
-        <v>5.318078226519759</v>
+        <v>6.04175391175121</v>
       </c>
       <c r="E17" t="n">
-        <v>19.20662737905037</v>
+        <v>19.45936850803167</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.749651123554581</v>
+        <v>1.441156542449105</v>
       </c>
       <c r="C18" t="n">
-        <v>14.41410815104505</v>
+        <v>14.17623068230605</v>
       </c>
       <c r="D18" t="n">
-        <v>5.672646227385537</v>
+        <v>6.389606758319941</v>
       </c>
       <c r="E18" t="n">
-        <v>21.83640550198517</v>
+        <v>22.00699398307509</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.734227867120863</v>
+        <v>1.423867965377319</v>
       </c>
       <c r="C19" t="n">
-        <v>15.39215466644685</v>
+        <v>15.17246898266755</v>
       </c>
       <c r="D19" t="n">
-        <v>5.731600177025559</v>
+        <v>6.455590021522369</v>
       </c>
       <c r="E19" t="n">
-        <v>22.85798271059327</v>
+        <v>23.05192696956723</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.901507858447477</v>
+        <v>1.558288861042792</v>
       </c>
       <c r="C20" t="n">
-        <v>17.54824933955961</v>
+        <v>17.38091044337074</v>
       </c>
       <c r="D20" t="n">
-        <v>6.088062950960533</v>
+        <v>6.81068816614844</v>
       </c>
       <c r="E20" t="n">
-        <v>25.53782014896762</v>
+        <v>25.74988747056198</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.114813788080423</v>
+        <v>0.9114643860997814</v>
       </c>
       <c r="C21" t="n">
-        <v>12.73699836535727</v>
+        <v>12.73162820541504</v>
       </c>
       <c r="D21" t="n">
-        <v>5.073092904402011</v>
+        <v>5.657998551638176</v>
       </c>
       <c r="E21" t="n">
-        <v>18.9249050578397</v>
+        <v>19.30109114315299</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_67_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_67_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.254984225573864</v>
+        <v>2.584685972762277</v>
       </c>
       <c r="C3" t="n">
-        <v>4.698081862150863</v>
+        <v>7.703182355958679</v>
       </c>
       <c r="D3" t="n">
-        <v>6.111757525737169</v>
+        <v>8.242525727941665</v>
       </c>
       <c r="E3" t="n">
-        <v>12.0648236134619</v>
+        <v>18.53039405666262</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.373441796763086</v>
+        <v>1.058016273672699</v>
       </c>
       <c r="C4" t="n">
-        <v>5.329897490122534</v>
+        <v>4.486706949872347</v>
       </c>
       <c r="D4" t="n">
-        <v>6.349152553621522</v>
+        <v>5.84815303715927</v>
       </c>
       <c r="E4" t="n">
-        <v>13.05249184050714</v>
+        <v>11.39287626070432</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.526948738202094</v>
+        <v>1.136660368094294</v>
       </c>
       <c r="C5" t="n">
-        <v>6.166801420282106</v>
+        <v>5.124008212472953</v>
       </c>
       <c r="D5" t="n">
-        <v>6.654394389025481</v>
+        <v>6.223073789640661</v>
       </c>
       <c r="E5" t="n">
-        <v>14.34814454750968</v>
+        <v>12.48374237020791</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.702397402004481</v>
+        <v>1.220657411570195</v>
       </c>
       <c r="C6" t="n">
-        <v>7.215844941211537</v>
+        <v>5.912964513795165</v>
       </c>
       <c r="D6" t="n">
-        <v>6.980876033912711</v>
+        <v>6.670944795595595</v>
       </c>
       <c r="E6" t="n">
-        <v>15.89911837712873</v>
+        <v>13.80456672096095</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.907450920612722</v>
+        <v>1.298136263602148</v>
       </c>
       <c r="C7" t="n">
-        <v>8.410482366352321</v>
+        <v>6.836450715384923</v>
       </c>
       <c r="D7" t="n">
-        <v>7.407536300812112</v>
+        <v>7.119053206206189</v>
       </c>
       <c r="E7" t="n">
-        <v>17.72546958777716</v>
+        <v>15.25364018519326</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.142854002831163</v>
+        <v>1.378118785873987</v>
       </c>
       <c r="C8" t="n">
-        <v>6.053361190429841</v>
+        <v>7.892676026866143</v>
       </c>
       <c r="D8" t="n">
-        <v>5.692852760021974</v>
+        <v>7.578886175646127</v>
       </c>
       <c r="E8" t="n">
-        <v>12.88906795328298</v>
+        <v>16.84968098838626</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.405225046978015</v>
+        <v>1.450664029864222</v>
       </c>
       <c r="C9" t="n">
-        <v>7.535759133048591</v>
+        <v>9.096413583574376</v>
       </c>
       <c r="D9" t="n">
-        <v>6.248807309824381</v>
+        <v>8.064202557280845</v>
       </c>
       <c r="E9" t="n">
-        <v>15.18979148985099</v>
+        <v>18.61128017071944</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.680698703831814</v>
+        <v>0.9299899652789185</v>
       </c>
       <c r="C10" t="n">
-        <v>9.188909120868754</v>
+        <v>6.751037175638404</v>
       </c>
       <c r="D10" t="n">
-        <v>6.769566374278499</v>
+        <v>6.366516052316055</v>
       </c>
       <c r="E10" t="n">
-        <v>17.63917419897907</v>
+        <v>14.04754319323338</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.94275814740336</v>
+        <v>0.8372049897505526</v>
       </c>
       <c r="C11" t="n">
-        <v>10.95153936054111</v>
+        <v>7.16565868357296</v>
       </c>
       <c r="D11" t="n">
-        <v>7.248515440234823</v>
+        <v>6.287171202858828</v>
       </c>
       <c r="E11" t="n">
-        <v>20.1428129481793</v>
+        <v>14.29003487618234</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.210565428930182</v>
+        <v>0.8757189521881548</v>
       </c>
       <c r="C12" t="n">
-        <v>12.82444417221617</v>
+        <v>8.454114188103516</v>
       </c>
       <c r="D12" t="n">
-        <v>7.699513585968435</v>
+        <v>6.820643087869502</v>
       </c>
       <c r="E12" t="n">
-        <v>22.73452318711479</v>
+        <v>16.15047622816117</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.450393552169631</v>
+        <v>0.6760020167132262</v>
       </c>
       <c r="C13" t="n">
-        <v>14.69164580939835</v>
+        <v>8.032483001560637</v>
       </c>
       <c r="D13" t="n">
-        <v>8.136632168959167</v>
+        <v>6.316142577611152</v>
       </c>
       <c r="E13" t="n">
-        <v>25.27867153052715</v>
+        <v>15.02462759588501</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.404154471476043</v>
+        <v>0.7127684682372692</v>
       </c>
       <c r="C14" t="n">
-        <v>10.25425659608751</v>
+        <v>9.386332720671076</v>
       </c>
       <c r="D14" t="n">
-        <v>6.172110371921102</v>
+        <v>6.753579902192403</v>
       </c>
       <c r="E14" t="n">
-        <v>17.83052143948466</v>
+        <v>16.85268109110075</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.419155576396935</v>
+        <v>0.6761100089606934</v>
       </c>
       <c r="C15" t="n">
-        <v>11.14070605068308</v>
+        <v>10.12735588783657</v>
       </c>
       <c r="D15" t="n">
-        <v>6.159504731398573</v>
+        <v>6.88682270061278</v>
       </c>
       <c r="E15" t="n">
-        <v>18.71936635847859</v>
+        <v>17.69028859741004</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.620109513979214</v>
+        <v>0.7265522060048946</v>
       </c>
       <c r="C16" t="n">
-        <v>13.19130211549748</v>
+        <v>11.80943331690784</v>
       </c>
       <c r="D16" t="n">
-        <v>6.560548668583396</v>
+        <v>7.369538229313894</v>
       </c>
       <c r="E16" t="n">
-        <v>21.37196029806009</v>
+        <v>19.90552375222663</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.285107744859075</v>
+        <v>0.4382619926528187</v>
       </c>
       <c r="C17" t="n">
-        <v>12.13250685142138</v>
+        <v>8.835690068313124</v>
       </c>
       <c r="D17" t="n">
-        <v>6.04175391175121</v>
+        <v>6.170588662979521</v>
       </c>
       <c r="E17" t="n">
-        <v>19.45936850803167</v>
+        <v>15.44454072394546</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.441156542449105</v>
+        <v>0.3286694964277472</v>
       </c>
       <c r="C18" t="n">
-        <v>14.17623068230605</v>
+        <v>7.807682412242204</v>
       </c>
       <c r="D18" t="n">
-        <v>6.389606758319941</v>
+        <v>5.689169041248012</v>
       </c>
       <c r="E18" t="n">
-        <v>22.00699398307509</v>
+        <v>13.82552094991796</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.423867965377319</v>
+        <v>0.3810261014952296</v>
       </c>
       <c r="C19" t="n">
-        <v>15.17246898266755</v>
+        <v>9.662871414003316</v>
       </c>
       <c r="D19" t="n">
-        <v>6.455590021522369</v>
+        <v>6.291716694729492</v>
       </c>
       <c r="E19" t="n">
-        <v>23.05192696956723</v>
+        <v>16.33561421022804</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.558288861042792</v>
+        <v>0.4328623802794612</v>
       </c>
       <c r="C20" t="n">
-        <v>17.38091044337074</v>
+        <v>11.62331358713673</v>
       </c>
       <c r="D20" t="n">
-        <v>6.81068816614844</v>
+        <v>6.849477017943232</v>
       </c>
       <c r="E20" t="n">
-        <v>25.74988747056198</v>
+        <v>18.90565298535942</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.9114643860997814</v>
+        <v>0.479878277835841</v>
       </c>
       <c r="C21" t="n">
-        <v>12.73162820541504</v>
+        <v>13.67711996694402</v>
       </c>
       <c r="D21" t="n">
-        <v>5.657998551638176</v>
+        <v>7.405745084646517</v>
       </c>
       <c r="E21" t="n">
-        <v>19.30109114315299</v>
+        <v>21.56274332942638</v>
       </c>
     </row>
   </sheetData>
